--- a/reports/顧客分析レポート.xlsx
+++ b/reports/顧客分析レポート.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\SQL_Projects\sakila_analysis\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\SQL_Projects\01_customer_analysis\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57932311-5E3C-499F-9F19-92EDD5AADD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA660B6-3537-41B6-8316-C348D07E276A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="650" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{AD36CDF6-FC1B-4EA5-8632-003BA67B2CC9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{AD36CDF6-FC1B-4EA5-8632-003BA67B2CC9}"/>
   </bookViews>
   <sheets>
     <sheet name="生データ" sheetId="1" r:id="rId1"/>
-    <sheet name="分析結果" sheetId="2" r:id="rId2"/>
+    <sheet name="分析結果" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="customer_id">生データ!$A:$A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="3" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>purchase_count</t>
   </si>
@@ -68,50 +68,43 @@
     <t>VIP</t>
   </si>
   <si>
-    <t>顧客レベル</t>
-  </si>
-  <si>
     <t>顧客数</t>
   </si>
   <si>
-    <t>売上合計</t>
+    <t>合計</t>
   </si>
   <si>
-    <t>【分析結果】</t>
+    <t>month</t>
   </si>
   <si>
-    <t>・ Regular 顧客は主力（349名、売上構成比 62.5%）</t>
+    <t>2005-05</t>
   </si>
   <si>
-    <t>・ VIP 顧客はわずか 46名だが、1人当たりの消費額が高い</t>
+    <t>2005-06</t>
   </si>
   <si>
-    <t>・ Low Value 顧客は 204名と多いが、売上貢献度は低い</t>
+    <t>2005-07</t>
   </si>
   <si>
-    <t>【提案】</t>
+    <t>2005-08</t>
   </si>
   <si>
-    <t>・ VIP 顧客向けに限定特典を提供</t>
+    <t>2006-02</t>
   </si>
   <si>
-    <t>・ Low Value 顧客にはクーポン施策でアップセルを促進</t>
+    <t>revenue</t>
   </si>
   <si>
-    <t>売上構成比</t>
-    <phoneticPr fontId="18"/>
+    <t>customer_level</t>
   </si>
   <si>
-    <t>合計</t>
+    <t>汇总</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.0%"/>
-  </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -698,21 +691,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -790,6 +777,323 @@
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="lt1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>分析結果!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>汇总</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>分析結果!$A$5:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Low Value</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Regular</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>VIP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>分析結果!$B$5:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>349</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F0DD-43A1-ACB9-F0E65175C778}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
@@ -797,7 +1101,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -810,8 +1114,8 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t>顧客レベル別の売上貢献度</a:t>
+              <a:rPr lang="ja-JP"/>
+              <a:t>利益貢献度</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -820,8 +1124,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.22500002743854589"/>
-          <c:y val="0.10083128887558303"/>
+          <c:x val="0.36959033245844264"/>
+          <c:y val="8.231262758821814E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -837,7 +1141,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -867,7 +1171,20 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="diamond"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -887,10 +1204,7 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="lt1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -900,8 +1214,9 @@
               <a:endParaRPr lang="ja-JP"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -943,10 +1258,7 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="lt1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -956,8 +1268,9 @@
               <a:endParaRPr lang="ja-JP"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -999,10 +1312,7 @@
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="lt1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -1012,120 +1322,7 @@
               <a:endParaRPr lang="ja-JP"/>
             </a:p>
           </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -1141,22 +1338,14 @@
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>分析結果!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>顧客数</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>汇总</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1185,10 +1374,7 @@
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="lt1"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1198,7 +1384,7 @@
                 <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -1211,14 +1397,13 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                    <a:ln w="9525">
                       <a:solidFill>
                         <a:schemeClr val="tx1">
                           <a:lumMod val="35000"/>
                           <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -1227,171 +1412,42 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
-              <c:f>分析結果!$A$2:$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Low Value</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Regular</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>VIP</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:strLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>Low Value</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Regular</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>VIP</c:v>
+              </c:pt>
+            </c:strLit>
           </c:cat>
           <c:val>
-            <c:numRef>
-              <c:f>分析結果!$B$2:$B$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>204</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>349</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>46</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>0.26202093683463462</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>0.625281574968371</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>0.11269748819699442</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-54CB-43D7-B2E4-C72BBBBC8BE9}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>分析結果!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>売上合計</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="ja-JP"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>分析結果!$A$2:$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Low Value</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Regular</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>VIP</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>分析結果!$C$2:$C$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>17661.930000000015</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>42148.080000000016</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7596.5499999999993</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-54CB-43D7-B2E4-C72BBBBC8BE9}"/>
+              <c16:uniqueId val="{00000000-F608-4C29-9B8B-58983B07F2A9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -1399,64 +1455,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="351260176"/>
-        <c:axId val="351260656"/>
+        <c:gapWidth val="79"/>
+        <c:overlap val="100"/>
+        <c:axId val="2052123392"/>
+        <c:axId val="2052108512"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="351260176"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="351260656"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="351260656"/>
+        <c:axId val="2052123392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1482,8 +1487,14 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1492,7 +1503,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1507,7 +1518,25 @@
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="351260176"/>
+        <c:crossAx val="2052108512"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2052108512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2052123392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1519,37 +1548,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -1563,7 +1561,7 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="lt1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -1591,26 +1589,11 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
+  <c:extLst/>
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
@@ -1623,17 +1606,60 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[顧客分析レポート.xlsx]分析結果!数据透视表1</c:name>
-    <c:fmtId val="13"/>
-  </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>月次売上推移</a:t>
+            </a:r>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.37971797478219532"/>
+          <c:y val="7.3227703661240054E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="accent4"/>
+        </a:solidFill>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -1642,19 +1668,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1666,15 +1689,29 @@
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
-          <a:ln w="19050">
+          <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="lt1"/>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="17"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1692,12 +1729,9 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="accent1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -1707,8 +1741,9 @@
               <a:endParaRPr lang="ja-JP"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1724,15 +1759,29 @@
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
-          <a:ln w="19050">
+          <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="lt1"/>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="17"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1750,12 +1799,9 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="accent1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -1765,8 +1811,9 @@
               <a:endParaRPr lang="ja-JP"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1779,333 +1826,289 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
+          <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="17"/>
+          <c:spPr>
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="7"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>分析結果!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>顧客数</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>汇总</c:v>
           </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="95000"/>
+                  <a:satMod val="105000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="17"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-9C44-4695-A44A-C6AA9BEA4997}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
+          </c:marker>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-9C44-4695-A44A-C6AA9BEA4997}"/>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-9C44-4695-A44A-C6AA9BEA4997}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
+          </c:dLbls>
           <c:cat>
-            <c:strRef>
-              <c:f>分析結果!$A$2:$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Low Value</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Regular</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>VIP</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:strLit>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>2005-05</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2005-06</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>2005-07</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>2005-08</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>2006-02</c:v>
+              </c:pt>
+            </c:strLit>
           </c:cat>
           <c:val>
-            <c:numRef>
-              <c:f>分析結果!$B$2:$B$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>204</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>349</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>46</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="5"/>
+              <c:pt idx="0">
+                <c:v>4823.4399999999996</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>9629.89</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>28368.91</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>24070.14</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>514.17999999999995</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AD61-4DAF-A177-A9932584A0B5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>分析結果!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>売上合計</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-9C44-4695-A44A-C6AA9BEA4997}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-9C44-4695-A44A-C6AA9BEA4997}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-9C44-4695-A44A-C6AA9BEA4997}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>分析結果!$A$2:$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Low Value</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Regular</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>VIP</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>分析結果!$C$2:$C$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>17661.930000000015</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>42148.080000000016</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7596.5499999999993</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AD61-4DAF-A177-A9932584A0B5}"/>
+              <c16:uniqueId val="{00000000-78A1-4196-BD95-44F62B0D79C9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="2052130112"/>
+        <c:axId val="2052128192"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2052130112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2052128192"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2052128192"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2052130112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2114,37 +2117,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -2158,11 +2130,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="lt1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="dk1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -2186,22 +2158,7 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
+  <c:extLst/>
 </c:chartSpace>
 </file>
 
@@ -2285,8 +2242,572 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="260">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="0"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="0"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="298">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2297,7 +2818,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -2320,18 +2841,18 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="bg1"/>
+        <a:schemeClr val="lt1"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
@@ -2343,19 +2864,16 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -2387,35 +2905,45 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="22225" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -2427,30 +2955,34 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -2472,15 +3004,13 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2495,15 +3025,15 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2514,17 +3044,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -2533,10 +3062,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
@@ -2552,21 +3081,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -2585,17 +3108,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -2604,17 +3126,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -2623,17 +3144,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -2654,7 +3174,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
@@ -2662,147 +3182,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -2824,386 +3207,16 @@
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
@@ -3224,7 +3237,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -3233,14 +3246,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -3254,27 +3267,26 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="800" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3288,6 +3300,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -3295,14 +3318,518 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="234">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr/>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9575">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+            <a:satMod val="105000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="17"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1440" b="0" kern="1200" cap="all" spc="0" baseline="0">
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -3312,22 +3839,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>466912</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>16492</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>183742</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>46692</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>177426</xdr:rowOff>
+      <xdr:colOff>117881</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>198795</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A79D7DC-FFC7-097C-AECC-BE4607E86BB3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1F35AC2-8E74-9601-0421-0515031D1241}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3347,27 +3874,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>553757</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>220076</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>436563</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>168672</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>97826</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>13956</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="图表 5">
+        <xdr:cNvPr id="4" name="图表 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{968F0B30-757A-DC56-6AED-E838CC92981F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{226ADEF5-2C07-482A-ADDE-44E3C7B08B6A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3376,6 +3905,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>112431</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>34742</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="图表 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EDF6362-617E-4CF6-BD8A-0D6DEB0A35DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7617,14 +8184,14 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{702458CA-C829-4815-AFA7-7446B0213F36}" name="数据透视表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" grandTotalCaption="合計" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="顧客レベル">
-  <location ref="A1:C5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21F9056F-AFB9-4960-A8E4-7AE0A505BBAD}" name="数据透视表1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" grandTotalCaption="合計" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A3:B8" firstHeaderRow="2" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
       <items count="4">
         <item x="1"/>
         <item x="0"/>
@@ -7650,126 +8217,18 @@
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
-  <dataFields count="2">
+  <dataFields count="1">
     <dataField name="顧客数" fld="0" subtotal="count" baseField="4" baseItem="0"/>
-    <dataField name="売上合計" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="10">
-    <chartFormat chart="0" format="3" series="1">
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -8104,7 +8563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDF41BFD-8D00-4216-9189-B132E7E040BD}">
-  <dimension ref="A1:E600"/>
+  <dimension ref="A1:H600"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="19.1640625" customWidth="1"/>
@@ -8114,7 +8573,7 @@
     <col min="5" max="5" width="23.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -8130,8 +8589,14 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8148,8 +8613,14 @@
         <f>IF(C2&gt;=150, "VIP", IF(C2&gt;=100, "Regular", "Low Value"))</f>
         <v>Regular</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2">
+        <v>4823.4399999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>2</v>
       </c>
@@ -8166,8 +8637,14 @@
         <f t="shared" ref="E3:E66" si="0">IF(C3&gt;=150, "VIP", IF(C3&gt;=100, "Regular", "Low Value"))</f>
         <v>Regular</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3">
+        <v>9629.89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>3</v>
       </c>
@@ -8184,8 +8661,14 @@
         <f t="shared" si="0"/>
         <v>Regular</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4">
+        <v>28368.91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8202,8 +8685,14 @@
         <f t="shared" si="0"/>
         <v>Low Value</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>24070.14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>5</v>
       </c>
@@ -8220,8 +8709,14 @@
         <f t="shared" si="0"/>
         <v>Regular</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>514.17999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8239,7 +8734,7 @@
         <v>Low Value</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8257,7 +8752,7 @@
         <v>VIP</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8275,7 +8770,7 @@
         <v>Low Value</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>9</v>
       </c>
@@ -8293,7 +8788,7 @@
         <v>Low Value</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>10</v>
       </c>
@@ -8311,7 +8806,7 @@
         <v>Low Value</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>11</v>
       </c>
@@ -8329,7 +8824,7 @@
         <v>Regular</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>12</v>
       </c>
@@ -8347,7 +8842,7 @@
         <v>Regular</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>13</v>
       </c>
@@ -8365,7 +8860,7 @@
         <v>Regular</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>14</v>
       </c>
@@ -8383,7 +8878,7 @@
         <v>Regular</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>15</v>
       </c>
@@ -18920,122 +19415,57 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8242A22C-5D7F-4D22-8339-1EFCAE9391A0}">
-  <dimension ref="A1:D35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6B46DB5-F087-4106-8933-50F2059272A0}">
+  <dimension ref="A3:B8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="9.9140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.4140625" customWidth="1"/>
-    <col min="3" max="3" width="17.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>204</v>
-      </c>
-      <c r="C2">
-        <v>17661.930000000015</v>
-      </c>
-      <c r="D2" s="3">
-        <f>C2/$C$5</f>
-        <v>0.26202093683463484</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>349</v>
-      </c>
-      <c r="C3">
-        <v>42148.080000000016</v>
-      </c>
-      <c r="D3" s="3">
-        <f t="shared" ref="D3:D4" si="0">C3/$C$5</f>
-        <v>0.62528157496837156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>46</v>
-      </c>
-      <c r="C4">
-        <v>7596.5499999999993</v>
-      </c>
-      <c r="D4" s="3">
-        <f t="shared" si="0"/>
-        <v>0.11269748819699452</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
+      <c r="B8" s="2">
         <v>599</v>
-      </c>
-      <c r="C5">
-        <v>67406.559999999969</v>
-      </c>
-      <c r="D5" s="3">
-        <f>SUM(D2:D4)</f>
-        <v>1.0000000000000009</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
